--- a/assets/photos.xlsx
+++ b/assets/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/70c9e965e0e1f885/Documents/blog/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="208" documentId="8_{49E107E2-FAE3-46D4-A586-0D8CBE2A2945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F89373D-4348-4C9D-951C-FD5E3B6A41DC}"/>
+  <xr:revisionPtr revIDLastSave="214" documentId="8_{49E107E2-FAE3-46D4-A586-0D8CBE2A2945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C09D425-2342-403E-98B8-6AE445724D80}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{A4FBE4D0-7B05-46E0-8DFD-C3559556203F}"/>
   </bookViews>
@@ -496,9 +496,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -622,496 +621,198 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:multiLvlStrRef>
+            <c:strRef>
               <c:f>images!$B$2:$F$33</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="32"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Concert du GP Explorer Last Race</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>SDM au GP Explorer Last Race</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Discours d'ouverture du QG de campagne de Rachida Dati</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>Discours d'ouverture du QG de campagne de Rachida Dati</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>Ouverture du QG de campagne municipale de Rachida Dati pour Paris</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Dernière de "Lamomali Tour" de 'M' à Bercy</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>Porte Ouverte EFJ : salon des écoles de journalisme</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>Campagne de Dati : Tractage</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>200 ans du Figaro : Concert de Patrick Bruel</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>200 ans du Figaro</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>Campagne de Dati : Visite des bars LGBT+</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>Campagne de Dati : Visite des bars LGBT+</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>Campagne de Dati : Rencontre des commercants du 12ème</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>Campagne de Dati : Visite d'un camps de sans abris à Paris Centre</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>Campagne de Dati : Visite d'un camps de sans abris à Paris Centre</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>Reportage à Rungis : Emarquement de viande</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>Halloween à Lille</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>Musée juif de Berlin</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>Plafond du parlement de Brelin</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>Fort épisode neigeux à Paris</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>Fort épisode neigeux à Paris</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>Conférence de Média En Seine</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>Procès en Appel de Marine Le Pen</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>Reportage à Rungis : Un boucher</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>Stand de la série HPI à la Braderie de Lille</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>Corrida : Torreau dans une arène</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>Reportage à Rungis : Dock de chargement</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>Studio EFJ</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>Studio EFJ</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>Emmaüs Défi : collecte de mobilier</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>IMG_0028.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>IMG_0043.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>IMG_0157.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>IMG_0159.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>IMG_0170.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>IMG_0178.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>IMG_0436.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>IMG_0546.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>IMG_0610.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>IMG_0631.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>IMG_0829.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>IMG_0865.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>IMG_0869.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>IMG_0901.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>IMG_0910.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>IMG_1036.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>IMG_1097.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>IMG_1238.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>IMG_1266.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>IMG_1411.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>IMG_1427.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>IMG_1584.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>IMG_1691.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>IMG_1846.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>IMG_1847.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>IMG_1917.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>IMG_3548.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>IMG_5390.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>P1031928.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>P1031986.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>P1031987.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>P1032031.JPG</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
+              <c:strCache>
+                <c:ptCount val="64"/>
+                <c:pt idx="0">
+                  <c:v>IMG_0028.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>IMG_0043.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>IMG_0157.JPG</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>IMG_0159.JPG</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>IMG_0170.JPG</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>IMG_0178.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>IMG_0436.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>IMG_0546.JPG</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>IMG_0610.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>IMG_0631.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>IMG_0829.JPG</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>IMG_0865.JPG</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>IMG_0869.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>IMG_0901.JPG</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>IMG_0910.JPG</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>IMG_1036.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>IMG_1097.JPG</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>IMG_1238.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>IMG_1266.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>IMG_1411.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>IMG_1427.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>IMG_1584.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>IMG_1691.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>IMG_1846.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>IMG_1847.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>IMG_1917.JPG</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>IMG_3548.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>IMG_5390.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>P1031928.JPG</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>P1031986.JPG</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>P1031987.JPG</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>P1032031.JPG</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Concert du GP Explorer Last Race</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>SDM au GP Explorer Last Race</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Discours d'ouverture du QG de campagne de Rachida Dati</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Discours d'ouverture du QG de campagne de Rachida Dati</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Ouverture du QG de campagne municipale de Rachida Dati pour Paris</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Dernière de "Lamomali Tour" de 'M' à Bercy</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Porte Ouverte EFJ : salon des écoles de journalisme</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>Campagne de Dati : Tractage</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>200 ans du Figaro : Concert de Patrick Bruel</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>200 ans du Figaro</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>Campagne de Dati : Visite des bars LGBT+</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>Campagne de Dati : Visite des bars LGBT+</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>Campagne de Dati : Rencontre des commercants du 12ème</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>Campagne de Dati : Visite d'un camps de sans abris à Paris Centre</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>Campagne de Dati : Visite d'un camps de sans abris à Paris Centre</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>Reportage à Rungis : Emarquement de viande</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>Halloween à Lille</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>Musée juif de Berlin</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>Plafond du parlement de Brelin</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>Fort épisode neigeux à Paris</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>Fort épisode neigeux à Paris</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>Conférence de Média En Seine</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>Procès en Appel de Marine Le Pen</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>Reportage à Rungis : Un boucher</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>Stand de la série HPI à la Braderie de Lille</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>Corrida : Torreau dans une arène</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>Reportage à Rungis : Dock de chargement</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>Studio EFJ</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>Studio EFJ</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>Emmaüs Défi : collecte de mobilier</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1243,496 +944,198 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:multiLvlStrRef>
+            <c:strRef>
               <c:f>images!$B$2:$F$33</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="32"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Concert du GP Explorer Last Race</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>SDM au GP Explorer Last Race</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Discours d'ouverture du QG de campagne de Rachida Dati</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>Discours d'ouverture du QG de campagne de Rachida Dati</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>Ouverture du QG de campagne municipale de Rachida Dati pour Paris</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Dernière de "Lamomali Tour" de 'M' à Bercy</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>Porte Ouverte EFJ : salon des écoles de journalisme</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>Campagne de Dati : Tractage</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>200 ans du Figaro : Concert de Patrick Bruel</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>200 ans du Figaro</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>Campagne de Dati : Visite des bars LGBT+</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>Campagne de Dati : Visite des bars LGBT+</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>Campagne de Dati : Rencontre des commercants du 12ème</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>Campagne de Dati : Visite d'un camps de sans abris à Paris Centre</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>Campagne de Dati : Visite d'un camps de sans abris à Paris Centre</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>Reportage à Rungis : Emarquement de viande</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>Halloween à Lille</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>Musée juif de Berlin</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>Plafond du parlement de Brelin</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>Fort épisode neigeux à Paris</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>Fort épisode neigeux à Paris</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>Conférence de Média En Seine</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>Procès en Appel de Marine Le Pen</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>Reportage à Rungis : Un boucher</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>Stand de la série HPI à la Braderie de Lille</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>Corrida : Torreau dans une arène</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>Reportage à Rungis : Dock de chargement</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>Studio EFJ</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>Studio EFJ</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>Emmaüs Défi : collecte de mobilier</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>IMG_0028.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>IMG_0043.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>IMG_0157.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>IMG_0159.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>IMG_0170.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>IMG_0178.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>IMG_0436.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>IMG_0546.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>IMG_0610.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>IMG_0631.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>IMG_0829.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>IMG_0865.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>IMG_0869.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>IMG_0901.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>IMG_0910.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>IMG_1036.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>IMG_1097.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>IMG_1238.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>IMG_1266.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>IMG_1411.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>IMG_1427.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>IMG_1584.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>IMG_1691.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>IMG_1846.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>IMG_1847.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>IMG_1917.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>IMG_3548.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>IMG_5390.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>P1031928.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>P1031986.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>P1031987.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>P1032031.JPG</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
+              <c:strCache>
+                <c:ptCount val="64"/>
+                <c:pt idx="0">
+                  <c:v>IMG_0028.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>IMG_0043.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>IMG_0157.JPG</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>IMG_0159.JPG</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>IMG_0170.JPG</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>IMG_0178.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>IMG_0436.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>IMG_0546.JPG</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>IMG_0610.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>IMG_0631.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>IMG_0829.JPG</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>IMG_0865.JPG</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>IMG_0869.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>IMG_0901.JPG</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>IMG_0910.JPG</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>IMG_1036.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>IMG_1097.JPG</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>IMG_1238.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>IMG_1266.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>IMG_1411.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>IMG_1427.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>IMG_1584.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>IMG_1691.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>IMG_1846.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>IMG_1847.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>IMG_1917.JPG</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>IMG_3548.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>IMG_5390.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>P1031928.JPG</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>P1031986.JPG</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>P1031987.JPG</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>P1032031.JPG</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Concert du GP Explorer Last Race</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>SDM au GP Explorer Last Race</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Discours d'ouverture du QG de campagne de Rachida Dati</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Discours d'ouverture du QG de campagne de Rachida Dati</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Ouverture du QG de campagne municipale de Rachida Dati pour Paris</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Dernière de "Lamomali Tour" de 'M' à Bercy</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Porte Ouverte EFJ : salon des écoles de journalisme</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>Campagne de Dati : Tractage</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>200 ans du Figaro : Concert de Patrick Bruel</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>200 ans du Figaro</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>Campagne de Dati : Visite des bars LGBT+</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>Campagne de Dati : Visite des bars LGBT+</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>Campagne de Dati : Rencontre des commercants du 12ème</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>Campagne de Dati : Visite d'un camps de sans abris à Paris Centre</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>Campagne de Dati : Visite d'un camps de sans abris à Paris Centre</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>Reportage à Rungis : Emarquement de viande</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>Halloween à Lille</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>Musée juif de Berlin</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>Plafond du parlement de Brelin</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>Fort épisode neigeux à Paris</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>Fort épisode neigeux à Paris</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>Conférence de Média En Seine</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>Procès en Appel de Marine Le Pen</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>Reportage à Rungis : Un boucher</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>Stand de la série HPI à la Braderie de Lille</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>Corrida : Torreau dans une arène</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>Reportage à Rungis : Dock de chargement</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>Studio EFJ</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>Studio EFJ</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>Emmaüs Défi : collecte de mobilier</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1864,496 +1267,198 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:multiLvlStrRef>
+            <c:strRef>
               <c:f>images!$B$2:$F$33</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="32"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Concert du GP Explorer Last Race</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>SDM au GP Explorer Last Race</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Discours d'ouverture du QG de campagne de Rachida Dati</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>Discours d'ouverture du QG de campagne de Rachida Dati</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>Ouverture du QG de campagne municipale de Rachida Dati pour Paris</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Dernière de "Lamomali Tour" de 'M' à Bercy</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>Porte Ouverte EFJ : salon des écoles de journalisme</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>Campagne de Dati : Tractage</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>200 ans du Figaro : Concert de Patrick Bruel</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>200 ans du Figaro</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>Campagne de Dati : Visite des bars LGBT+</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>Campagne de Dati : Visite des bars LGBT+</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>Campagne de Dati : Rencontre des commercants du 12ème</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>Campagne de Dati : Visite d'un camps de sans abris à Paris Centre</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>Campagne de Dati : Visite d'un camps de sans abris à Paris Centre</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>Reportage à Rungis : Emarquement de viande</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>Halloween à Lille</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>Musée juif de Berlin</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>Plafond du parlement de Brelin</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>Fort épisode neigeux à Paris</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>Fort épisode neigeux à Paris</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>Conférence de Média En Seine</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>Procès en Appel de Marine Le Pen</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>Reportage à Rungis : Un boucher</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>Stand de la série HPI à la Braderie de Lille</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>Corrida : Torreau dans une arène</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>Reportage à Rungis : Dock de chargement</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>Studio EFJ</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>Studio EFJ</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>Emmaüs Défi : collecte de mobilier</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>IMG_0028.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>IMG_0043.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>IMG_0157.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>IMG_0159.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>IMG_0170.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>IMG_0178.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>IMG_0436.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>IMG_0546.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>IMG_0610.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>IMG_0631.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>IMG_0829.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>IMG_0865.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>IMG_0869.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>IMG_0901.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>IMG_0910.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>IMG_1036.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>IMG_1097.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>IMG_1238.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>IMG_1266.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>IMG_1411.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>IMG_1427.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>IMG_1584.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>IMG_1691.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>IMG_1846.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>IMG_1847.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>IMG_1917.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>IMG_3548.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>IMG_5390.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>P1031928.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>P1031986.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>P1031987.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>P1032031.JPG</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
+              <c:strCache>
+                <c:ptCount val="64"/>
+                <c:pt idx="0">
+                  <c:v>IMG_0028.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>IMG_0043.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>IMG_0157.JPG</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>IMG_0159.JPG</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>IMG_0170.JPG</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>IMG_0178.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>IMG_0436.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>IMG_0546.JPG</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>IMG_0610.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>IMG_0631.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>IMG_0829.JPG</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>IMG_0865.JPG</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>IMG_0869.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>IMG_0901.JPG</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>IMG_0910.JPG</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>IMG_1036.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>IMG_1097.JPG</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>IMG_1238.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>IMG_1266.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>IMG_1411.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>IMG_1427.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>IMG_1584.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>IMG_1691.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>IMG_1846.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>IMG_1847.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>IMG_1917.JPG</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>IMG_3548.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>IMG_5390.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>P1031928.JPG</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>P1031986.JPG</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>P1031987.JPG</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>P1032031.JPG</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Concert du GP Explorer Last Race</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>SDM au GP Explorer Last Race</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Discours d'ouverture du QG de campagne de Rachida Dati</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Discours d'ouverture du QG de campagne de Rachida Dati</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Ouverture du QG de campagne municipale de Rachida Dati pour Paris</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Dernière de "Lamomali Tour" de 'M' à Bercy</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Porte Ouverte EFJ : salon des écoles de journalisme</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>Campagne de Dati : Tractage</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>200 ans du Figaro : Concert de Patrick Bruel</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>200 ans du Figaro</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>Campagne de Dati : Visite des bars LGBT+</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>Campagne de Dati : Visite des bars LGBT+</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>Campagne de Dati : Rencontre des commercants du 12ème</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>Campagne de Dati : Visite d'un camps de sans abris à Paris Centre</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>Campagne de Dati : Visite d'un camps de sans abris à Paris Centre</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>Reportage à Rungis : Emarquement de viande</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>Halloween à Lille</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>Musée juif de Berlin</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>Plafond du parlement de Brelin</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>Fort épisode neigeux à Paris</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>Fort épisode neigeux à Paris</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>Conférence de Média En Seine</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>Procès en Appel de Marine Le Pen</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>Reportage à Rungis : Un boucher</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>Stand de la série HPI à la Braderie de Lille</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>Corrida : Torreau dans une arène</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>Reportage à Rungis : Dock de chargement</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>Studio EFJ</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>Studio EFJ</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>Emmaüs Défi : collecte de mobilier</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -2485,597 +1590,202 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:multiLvlStrRef>
+            <c:strRef>
               <c:f>images!$B$2:$F$33</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="32"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Concert du GP Explorer Last Race</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>SDM au GP Explorer Last Race</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Discours d'ouverture du QG de campagne de Rachida Dati</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>Discours d'ouverture du QG de campagne de Rachida Dati</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>Ouverture du QG de campagne municipale de Rachida Dati pour Paris</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Dernière de "Lamomali Tour" de 'M' à Bercy</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>Porte Ouverte EFJ : salon des écoles de journalisme</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>Campagne de Dati : Tractage</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>200 ans du Figaro : Concert de Patrick Bruel</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>200 ans du Figaro</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>Campagne de Dati : Visite des bars LGBT+</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>Campagne de Dati : Visite des bars LGBT+</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>Campagne de Dati : Rencontre des commercants du 12ème</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>Campagne de Dati : Visite d'un camps de sans abris à Paris Centre</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>Campagne de Dati : Visite d'un camps de sans abris à Paris Centre</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>Reportage à Rungis : Emarquement de viande</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>Halloween à Lille</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>Musée juif de Berlin</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>Plafond du parlement de Brelin</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>Fort épisode neigeux à Paris</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>Fort épisode neigeux à Paris</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>Conférence de Média En Seine</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>Procès en Appel de Marine Le Pen</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>Reportage à Rungis : Un boucher</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>Stand de la série HPI à la Braderie de Lille</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>Corrida : Torreau dans une arène</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>Reportage à Rungis : Dock de chargement</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>Studio EFJ</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>Studio EFJ</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>Emmaüs Défi : collecte de mobilier</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>C:\Users\align\OneDrive\Documents\blog\assets\images\</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>18/03/2026 15:29</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>.JPG</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>IMG_0028.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>IMG_0043.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>IMG_0157.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>IMG_0159.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>IMG_0170.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>IMG_0178.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>IMG_0436.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>IMG_0546.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>IMG_0610.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>IMG_0631.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>IMG_0829.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>IMG_0865.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>IMG_0869.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>IMG_0901.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>IMG_0910.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>IMG_1036.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>IMG_1097.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>IMG_1238.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>IMG_1266.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>IMG_1411.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>IMG_1427.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>IMG_1584.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>IMG_1691.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>IMG_1846.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>IMG_1847.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>IMG_1917.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>IMG_3548.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>IMG_5390.JPEG</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>P1031928.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>P1031986.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>P1031987.JPG</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>P1032031.JPG</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
+              <c:strCache>
+                <c:ptCount val="64"/>
+                <c:pt idx="0">
+                  <c:v>IMG_0028.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>IMG_0043.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>IMG_0157.JPG</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>IMG_0159.JPG</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>IMG_0170.JPG</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>IMG_0178.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>IMG_0436.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>IMG_0546.JPG</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>IMG_0610.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>IMG_0631.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>IMG_0829.JPG</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>IMG_0865.JPG</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>IMG_0869.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>IMG_0901.JPG</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>IMG_0910.JPG</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>IMG_1036.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>IMG_1097.JPG</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>IMG_1238.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>IMG_1266.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>IMG_1411.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>IMG_1427.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>IMG_1584.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>IMG_1691.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>IMG_1846.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>IMG_1847.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>IMG_1917.JPG</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>IMG_3548.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>IMG_5390.JPEG</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>P1031928.JPG</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>P1031986.JPG</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>P1031987.JPG</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>P1032031.JPG</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Concert du GP Explorer Last Race</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>SDM au GP Explorer Last Race</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Discours d'ouverture du QG de campagne de Rachida Dati</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Discours d'ouverture du QG de campagne de Rachida Dati</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Ouverture du QG de campagne municipale de Rachida Dati pour Paris</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Dernière de "Lamomali Tour" de 'M' à Bercy</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Porte Ouverte EFJ : salon des écoles de journalisme</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>Campagne de Dati : Tractage</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>200 ans du Figaro : Concert de Patrick Bruel</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>200 ans du Figaro</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>Campagne de Dati : Visite des bars LGBT+</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>Campagne de Dati : Visite des bars LGBT+</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>Campagne de Dati : Rencontre des commercants du 12ème</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>Campagne de Dati : Visite d'un camps de sans abris à Paris Centre</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>Campagne de Dati : Visite d'un camps de sans abris à Paris Centre</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>Reportage à Rungis : Emarquement de viande</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>Halloween à Lille</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>Musée juif de Berlin</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>Plafond du parlement de Brelin</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>Fort épisode neigeux à Paris</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>Fort épisode neigeux à Paris</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>Conférence de Média En Seine</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>Procès en Appel de Marine Le Pen</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>Reportage à Rungis : Un boucher</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>Stand de la série HPI à la Braderie de Lille</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>Corrida : Torreau dans une arène</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>Reportage à Rungis : Dock de chargement</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>Studio EFJ</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>Studio EFJ</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>Emmaüs Défi : collecte de mobilier</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>images!$J$2:$J$33</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -3866,6 +2576,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="DonnéesExternes_1" connectionId="1" xr16:uid="{C7E9F4C8-39B0-4223-B46D-95BD0A5CB8B4}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="11" unboundColumnsRight="5">
@@ -4286,17 +3000,18 @@
   <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="3"/>
+    <col min="1" max="1" width="11.5546875" style="2"/>
     <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" customWidth="1"/>
-    <col min="5" max="5" width="52.33203125" customWidth="1"/>
-    <col min="6" max="6" width="34.21875" customWidth="1"/>
-    <col min="7" max="7" width="41.44140625" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="52.33203125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" customWidth="1"/>
+    <col min="10" max="10" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B1" t="s">
@@ -4328,1130 +3043,1121 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" cm="1">
+      <c r="A2" s="2" cm="1">
         <f t="array" ref="A2:A51">_xlfn.SEQUENCE(50)</f>
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>46099.645671840277</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>61</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="1" t="e" vm="1">
+      <c r="J2" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT("images/" &amp; images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>46099.645672094906</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>60</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
       </c>
-      <c r="J3" s="1" t="e" vm="1">
+      <c r="J3" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>46099.645672280094</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>53</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>59</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" t="s">
         <v>54</v>
       </c>
-      <c r="J4" s="1" t="e" vm="1">
+      <c r="J4" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>46099.64567247685</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" t="s">
         <v>59</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="1" t="e" vm="1">
+      <c r="J5" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>46099.645672662038</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>55</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>56</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" t="s">
         <v>59</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" t="s">
         <v>54</v>
       </c>
-      <c r="J6" s="1" t="e" vm="1">
+      <c r="J6" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>46099.645672847226</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>66</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" t="s">
         <v>58</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="1" t="e" vm="1">
+      <c r="J7" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>46099.64567302083</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="1" t="e" vm="1">
+      <c r="J8" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>46099.645673194442</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>67</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" t="s">
         <v>68</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="1" t="e" vm="1">
+      <c r="J9" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <v>46099.645673379629</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" t="s">
         <v>71</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" t="s">
         <v>72</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" t="s">
         <v>48</v>
       </c>
-      <c r="J10" s="1" t="e" vm="1">
+      <c r="J10" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>46099.645673576386</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" t="s">
         <v>73</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" t="s">
         <v>72</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="1" t="e" vm="1">
+      <c r="J11" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>46099.645673738429</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" t="s">
         <v>75</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" t="s">
         <v>76</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" t="s">
         <v>77</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" t="s">
         <v>54</v>
       </c>
-      <c r="J12" s="1" t="e" vm="1">
+      <c r="J12" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>46099.645673946761</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" t="s">
         <v>75</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" t="s">
         <v>80</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" t="s">
         <v>77</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" t="s">
         <v>54</v>
       </c>
-      <c r="J13" s="1" t="e" vm="1">
+      <c r="J13" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>46099.645674131942</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" t="s">
         <v>78</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" t="s">
         <v>79</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" t="s">
         <v>81</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="1" t="e" vm="1">
+      <c r="J14" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>46099.645674305553</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" t="s">
         <v>82</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" t="s">
         <v>83</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" t="s">
         <v>84</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" t="s">
         <v>54</v>
       </c>
-      <c r="J15" s="1" t="e" vm="1">
+      <c r="J15" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <v>46099.645674502317</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" t="s">
         <v>82</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" t="s">
         <v>83</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" t="s">
         <v>84</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" t="s">
         <v>54</v>
       </c>
-      <c r="J16" s="1" t="e" vm="1">
+      <c r="J16" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="1">
         <v>46099.645674699073</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" t="s">
         <v>86</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" t="s">
         <v>87</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" t="s">
         <v>88</v>
       </c>
-      <c r="J17" s="1" t="e" vm="1">
+      <c r="J17" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="1">
         <v>46099.645674872685</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" t="s">
         <v>89</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" t="s">
         <v>90</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" t="s">
         <v>91</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" t="s">
         <v>88</v>
       </c>
-      <c r="J18" s="1" t="e" vm="1">
+      <c r="J18" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="1">
         <v>46099.645675057873</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" t="s">
         <v>92</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" t="s">
         <v>93</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" t="s">
         <v>94</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" t="s">
         <v>48</v>
       </c>
-      <c r="J19" s="1" t="e" vm="1">
+      <c r="J19" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="1">
         <v>46099.645675219908</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" t="s">
         <v>95</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" t="s">
         <v>96</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" t="s">
         <v>94</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" t="s">
         <v>48</v>
       </c>
-      <c r="J20" s="1" t="e" vm="1">
+      <c r="J20" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="1">
         <v>46099.645675405096</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" t="s">
         <v>97</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" t="s">
         <v>98</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" t="s">
         <v>99</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" t="s">
         <v>88</v>
       </c>
-      <c r="J21" s="1" t="e" vm="1">
+      <c r="J21" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="1">
         <v>46099.64567568287</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" t="s">
         <v>97</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" t="s">
         <v>98</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" t="s">
         <v>99</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" t="s">
         <v>88</v>
       </c>
-      <c r="J22" s="1" t="e" vm="1">
+      <c r="J22" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="1">
         <v>46099.6456759375</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" t="s">
         <v>100</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" t="s">
         <v>101</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" t="s">
         <v>102</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" t="s">
         <v>69</v>
       </c>
-      <c r="J23" s="1" t="e" vm="1">
+      <c r="J23" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="1">
         <v>46099.645676180553</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" t="s">
         <v>103</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" t="s">
         <v>104</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" t="s">
         <v>105</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" t="s">
         <v>54</v>
       </c>
-      <c r="J24" s="1" t="e" vm="1">
+      <c r="J24" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
+      <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="1">
         <v>46099.645676412038</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="1">
         <v>46099.645676655091</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1" t="e" vm="1">
+      <c r="J26" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
+      <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="1">
         <v>46099.645676886576</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" t="s">
         <v>12</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" t="s">
         <v>106</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" t="s">
         <v>107</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" t="s">
         <v>87</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I27" t="s">
         <v>88</v>
       </c>
-      <c r="J27" s="1" t="e" vm="1">
+      <c r="J27" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>11</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="1">
         <v>46099.645677141205</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" t="s">
         <v>12</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" t="s">
         <v>108</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" t="s">
         <v>109</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" t="s">
         <v>110</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" t="s">
         <v>48</v>
       </c>
-      <c r="J28" s="1" t="e" vm="1">
+      <c r="J28" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
+      <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="1">
         <v>46099.645677418979</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" t="s">
         <v>12</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" t="s">
         <v>111</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" t="s">
         <v>112</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" t="s">
         <v>113</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I29" t="s">
         <v>48</v>
       </c>
-      <c r="J29" s="1" t="e" vm="1">
+      <c r="J29" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="1">
         <v>46099.64567766204</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" t="s">
         <v>12</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" t="s">
         <v>114</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" t="s">
         <v>115</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" t="s">
         <v>87</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" t="s">
         <v>88</v>
       </c>
-      <c r="J30" s="1" t="e" vm="1">
+      <c r="J30" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="3">
+      <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s">
         <v>15</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="1">
         <v>46099.645677835651</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" t="s">
         <v>116</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" t="s">
         <v>117</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" t="s">
         <v>118</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" t="s">
         <v>69</v>
       </c>
-      <c r="J31" s="1" t="e" vm="1">
+      <c r="J31" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="3">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="1">
         <v>46099.645678067129</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" t="s">
         <v>12</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" t="s">
         <v>116</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" t="s">
         <v>119</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" t="s">
         <v>118</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I32" t="s">
         <v>69</v>
       </c>
-      <c r="J32" s="1" t="e" vm="1">
+      <c r="J32" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="3">
+      <c r="A33" s="2">
         <v>32</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="1">
         <v>46099.645678275461</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" t="s">
         <v>12</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" t="s">
         <v>120</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" t="s">
         <v>121</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" t="s">
         <v>122</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" t="s">
         <v>88</v>
       </c>
-      <c r="J33" s="1" t="e" vm="1">
+      <c r="J33" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT(images[[#This Row],[Folder Path]],"\",images[[#This Row],[Name]]),,0,,)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="3">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="3">
+      <c r="A35" s="2">
         <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="3">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="3">
+      <c r="A37" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="3">
+      <c r="A38" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="3">
+      <c r="A39" s="2">
         <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="3">
+      <c r="A40" s="2">
         <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="3">
+      <c r="A41" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="3">
+      <c r="A42" s="2">
         <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="3">
+      <c r="A43" s="2">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="3">
+      <c r="A44" s="2">
         <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="3">
+      <c r="A45" s="2">
         <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="3">
+      <c r="A46" s="2">
         <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="3">
+      <c r="A47" s="2">
         <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="3">
+      <c r="A48" s="2">
         <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="3">
+      <c r="A49" s="2">
         <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="3">
+      <c r="A50" s="2">
         <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="3">
+      <c r="A51" s="2">
         <v>50</v>
       </c>
     </row>
